--- a/artfynd/A 5851-2025 artfynd.xlsx
+++ b/artfynd/A 5851-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>130157685</v>
       </c>
       <c r="B4" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5851-2025 artfynd.xlsx
+++ b/artfynd/A 5851-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>130157685</v>
       </c>
       <c r="B4" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130157695</v>
       </c>
       <c r="B5" t="n">
-        <v>80235</v>
+        <v>80320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>130157691</v>
       </c>
       <c r="B6" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>130157688</v>
       </c>
       <c r="B7" t="n">
-        <v>80201</v>
+        <v>80286</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>130157692</v>
       </c>
       <c r="B8" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5851-2025 artfynd.xlsx
+++ b/artfynd/A 5851-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>130157685</v>
       </c>
       <c r="B4" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130157695</v>
       </c>
       <c r="B5" t="n">
-        <v>80320</v>
+        <v>80323</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>130157691</v>
       </c>
       <c r="B6" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>130157688</v>
       </c>
       <c r="B7" t="n">
-        <v>80286</v>
+        <v>80289</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>130157692</v>
       </c>
       <c r="B8" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5851-2025 artfynd.xlsx
+++ b/artfynd/A 5851-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>130157685</v>
       </c>
       <c r="B4" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130157695</v>
       </c>
       <c r="B5" t="n">
-        <v>80323</v>
+        <v>80349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>130157691</v>
       </c>
       <c r="B6" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>130157688</v>
       </c>
       <c r="B7" t="n">
-        <v>80289</v>
+        <v>80315</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>130157692</v>
       </c>
       <c r="B8" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5851-2025 artfynd.xlsx
+++ b/artfynd/A 5851-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>130157685</v>
       </c>
       <c r="B4" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5851-2025 artfynd.xlsx
+++ b/artfynd/A 5851-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>130157685</v>
       </c>
       <c r="B4" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5851-2025 artfynd.xlsx
+++ b/artfynd/A 5851-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80118696</v>
+        <v>130157685</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Örskölen, Dlr</t>
+          <t>Örsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413421.8037421083</v>
+        <v>413529</v>
       </c>
       <c r="R2" t="n">
-        <v>6712653.548137985</v>
+        <v>6712685</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,19 +754,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -794,12 +775,7 @@
         <v>80118695</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413464.2996031601</v>
+        <v>413464</v>
       </c>
       <c r="R3" t="n">
-        <v>6712657.451458428</v>
+        <v>6712657</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,19 +843,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130157685</v>
+        <v>130157688</v>
       </c>
       <c r="B4" t="n">
-        <v>97197</v>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413529</v>
+        <v>413464</v>
       </c>
       <c r="R4" t="n">
-        <v>6712685</v>
+        <v>6712702</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1004,27 +970,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130157695</v>
+        <v>80118696</v>
       </c>
       <c r="B5" t="n">
-        <v>80349</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1033,19 +999,22 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Örsåsen, Dlr</t>
+          <t>Örskölen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413471</v>
+        <v>413422</v>
       </c>
       <c r="R5" t="n">
-        <v>6712688</v>
+        <v>6712654</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,12 +1038,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,50 +1052,51 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130157691</v>
+        <v>130157693</v>
       </c>
       <c r="B6" t="n">
-        <v>80314</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>413468</v>
+        <v>413506</v>
       </c>
       <c r="R6" t="n">
-        <v>6712697</v>
+        <v>6712729</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1198,10 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130157688</v>
+        <v>130157692</v>
       </c>
       <c r="B7" t="n">
-        <v>80315</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,21 +1179,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>413464</v>
+        <v>413452</v>
       </c>
       <c r="R7" t="n">
-        <v>6712702</v>
+        <v>6712669</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1295,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130157692</v>
+        <v>130157691</v>
       </c>
       <c r="B8" t="n">
-        <v>78966</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1306,21 +1276,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1330,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413452</v>
+        <v>413468</v>
       </c>
       <c r="R8" t="n">
-        <v>6712669</v>
+        <v>6712697</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,6 +1359,103 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130157695</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Örsåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>413471</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6712688</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5851-2025 artfynd.xlsx
+++ b/artfynd/A 5851-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130157685</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80118695</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130157688</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80118696</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130157693</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130157692</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130157691</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,8 +1496,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130157695</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>